--- a/wfcv_avg_metrics_by_product.xlsx
+++ b/wfcv_avg_metrics_by_product.xlsx
@@ -456,7 +456,7 @@
         <v>36.55666687222686</v>
       </c>
       <c r="C2" t="n">
-        <v>9705.98752058589</v>
+        <v>9705.987520585888</v>
       </c>
       <c r="D2" t="n">
         <v>186024740.3994853</v>
@@ -614,7 +614,7 @@
         <v>69913.47343221511</v>
       </c>
       <c r="D2" t="n">
-        <v>7529642289.848586</v>
+        <v>7529642289.848584</v>
       </c>
       <c r="E2" t="n">
         <v>78570.03581057476</v>
@@ -924,7 +924,7 @@
         <v>3742.066239795138</v>
       </c>
       <c r="D2" t="n">
-        <v>21871824.21105035</v>
+        <v>21871824.21105034</v>
       </c>
       <c r="E2" t="n">
         <v>4132.457243307836</v>

--- a/wfcv_avg_metrics_by_product.xlsx
+++ b/wfcv_avg_metrics_by_product.xlsx
@@ -456,7 +456,7 @@
         <v>36.55666687222686</v>
       </c>
       <c r="C2" t="n">
-        <v>9705.987520585888</v>
+        <v>9705.987520585892</v>
       </c>
       <c r="D2" t="n">
         <v>186024740.3994853</v>
@@ -614,7 +614,7 @@
         <v>69913.47343221511</v>
       </c>
       <c r="D2" t="n">
-        <v>7529642289.848584</v>
+        <v>7529642289.848586</v>
       </c>
       <c r="E2" t="n">
         <v>78570.03581057476</v>
@@ -921,13 +921,13 @@
         <v>18.31881976591612</v>
       </c>
       <c r="C2" t="n">
-        <v>3742.066239795138</v>
+        <v>3742.066239795137</v>
       </c>
       <c r="D2" t="n">
         <v>21871824.21105034</v>
       </c>
       <c r="E2" t="n">
-        <v>4132.457243307836</v>
+        <v>4132.457243307835</v>
       </c>
     </row>
     <row r="3">

--- a/wfcv_avg_metrics_by_product.xlsx
+++ b/wfcv_avg_metrics_by_product.xlsx
@@ -453,16 +453,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.55666687222686</v>
+        <v>16.56292034153594</v>
       </c>
       <c r="C2" t="n">
-        <v>9705.987520585892</v>
+        <v>5895.55718881754</v>
       </c>
       <c r="D2" t="n">
-        <v>186024740.3994853</v>
+        <v>71925541.9965318</v>
       </c>
       <c r="E2" t="n">
-        <v>10943.06438636262</v>
+        <v>7180.336925037693</v>
       </c>
     </row>
     <row r="3">
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.12810145884438</v>
+        <v>15.75005865297732</v>
       </c>
       <c r="C3" t="n">
-        <v>9379.336647727272</v>
+        <v>5103.331380208333</v>
       </c>
       <c r="D3" t="n">
-        <v>226958098.821966</v>
+        <v>83646539.62913133</v>
       </c>
       <c r="E3" t="n">
-        <v>11216.76915754793</v>
+        <v>6953.54145578972</v>
       </c>
     </row>
     <row r="4">
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.88543417751098</v>
+        <v>21.45444279815172</v>
       </c>
       <c r="C4" t="n">
-        <v>11745.21070382014</v>
+        <v>8587.703835424498</v>
       </c>
       <c r="D4" t="n">
-        <v>211409724.6861337</v>
+        <v>104229530.9350453</v>
       </c>
       <c r="E4" t="n">
-        <v>12610.45110807058</v>
+        <v>9346.935716175638</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.07036379919701</v>
+        <v>22.24515096963352</v>
       </c>
       <c r="C5" t="n">
-        <v>10738.0953274544</v>
+        <v>8124.630678813137</v>
       </c>
       <c r="D5" t="n">
-        <v>216220660.939234</v>
+        <v>131983778.0173983</v>
       </c>
       <c r="E5" t="n">
-        <v>12503.14328127759</v>
+        <v>9787.687362678971</v>
       </c>
     </row>
     <row r="6">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>622.846498481687</v>
+        <v>31.69207572272781</v>
       </c>
       <c r="C6" t="n">
-        <v>138081.0305811948</v>
+        <v>13289.6808687801</v>
       </c>
       <c r="D6" t="n">
-        <v>92083736985.0629</v>
+        <v>351937995.4273841</v>
       </c>
       <c r="E6" t="n">
-        <v>162411.2538881838</v>
+        <v>15054.81226623002</v>
       </c>
     </row>
     <row r="7">
@@ -548,16 +548,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.92008349620892</v>
+        <v>25.12884818267521</v>
       </c>
       <c r="C7" t="n">
-        <v>14623.90909090909</v>
+        <v>10913.25</v>
       </c>
       <c r="D7" t="n">
-        <v>352618422.030303</v>
+        <v>182247489.4166667</v>
       </c>
       <c r="E7" t="n">
-        <v>15782.0619446796</v>
+        <v>11775.92199606104</v>
       </c>
     </row>
   </sheetData>
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.05448607558924</v>
+        <v>19.42843534392942</v>
       </c>
       <c r="C2" t="n">
-        <v>69913.47343221511</v>
+        <v>52064.49553607679</v>
       </c>
       <c r="D2" t="n">
-        <v>7529642289.848586</v>
+        <v>4077107770.738763</v>
       </c>
       <c r="E2" t="n">
-        <v>78570.03581057476</v>
+        <v>61515.47045434544</v>
       </c>
     </row>
     <row r="3">
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.47599464573716</v>
+        <v>24.23758790282074</v>
       </c>
       <c r="C3" t="n">
-        <v>76039.87050189394</v>
+        <v>69390.7177734375</v>
       </c>
       <c r="D3" t="n">
-        <v>7959933542.231491</v>
+        <v>6527652256.345076</v>
       </c>
       <c r="E3" t="n">
-        <v>85097.77076636924</v>
+        <v>77576.46916282372</v>
       </c>
     </row>
     <row r="4">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.77348055163633</v>
+        <v>31.89393019065162</v>
       </c>
       <c r="C4" t="n">
-        <v>84999.47964602501</v>
+        <v>85410.77590115143</v>
       </c>
       <c r="D4" t="n">
-        <v>9373327989.769497</v>
+        <v>9647461440.113342</v>
       </c>
       <c r="E4" t="n">
-        <v>94484.08936539054</v>
+        <v>96103.89196230404</v>
       </c>
     </row>
     <row r="5">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.77476751666122</v>
+        <v>29.83795495531777</v>
       </c>
       <c r="C5" t="n">
-        <v>74247.59724741369</v>
+        <v>73368.05284216917</v>
       </c>
       <c r="D5" t="n">
-        <v>8053498268.179462</v>
+        <v>8148750009.512897</v>
       </c>
       <c r="E5" t="n">
-        <v>82052.09060361095</v>
+        <v>81616.13784592992</v>
       </c>
     </row>
     <row r="6">
@@ -684,16 +684,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>395.5309852365625</v>
+        <v>51.98865116295553</v>
       </c>
       <c r="C6" t="n">
-        <v>801750.5704114438</v>
+        <v>130821.0770874356</v>
       </c>
       <c r="D6" t="n">
-        <v>2749500332174.795</v>
+        <v>31230519741.51707</v>
       </c>
       <c r="E6" t="n">
-        <v>955420.0090367924</v>
+        <v>148975.8411224502</v>
       </c>
     </row>
     <row r="7">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.83640482618178</v>
+        <v>22.44291560207185</v>
       </c>
       <c r="C7" t="n">
-        <v>91017.1102483538</v>
+        <v>67554.45648664807</v>
       </c>
       <c r="D7" t="n">
-        <v>13419581937.27197</v>
+        <v>7375640250.677624</v>
       </c>
       <c r="E7" t="n">
-        <v>98076.34217869039</v>
+        <v>74943.18885779358</v>
       </c>
     </row>
   </sheetData>
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.55008204348383</v>
+        <v>9.536792199409831</v>
       </c>
       <c r="C2" t="n">
-        <v>74857.93906752054</v>
+        <v>47318.74948368828</v>
       </c>
       <c r="D2" t="n">
-        <v>9357744005.700563</v>
+        <v>2970946454.983293</v>
       </c>
       <c r="E2" t="n">
-        <v>81707.4849908132</v>
+        <v>53512.49706818607</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.25853395808771</v>
+        <v>9.861608872262215</v>
       </c>
       <c r="C3" t="n">
-        <v>68248.16003787878</v>
+        <v>47739.3203125</v>
       </c>
       <c r="D3" t="n">
-        <v>6883151798.722332</v>
+        <v>3072523026.308919</v>
       </c>
       <c r="E3" t="n">
-        <v>74732.63571085891</v>
+        <v>55150.49658985708</v>
       </c>
     </row>
     <row r="4">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.57545901157206</v>
+        <v>10.79901883596843</v>
       </c>
       <c r="C4" t="n">
-        <v>63509.86255543624</v>
+        <v>55428.0231086014</v>
       </c>
       <c r="D4" t="n">
-        <v>5572182827.08509</v>
+        <v>3764220029.346425</v>
       </c>
       <c r="E4" t="n">
-        <v>69657.88165833971</v>
+        <v>57999.41995821928</v>
       </c>
     </row>
     <row r="5">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.99830669911734</v>
+        <v>14.76406970168307</v>
       </c>
       <c r="C5" t="n">
-        <v>88035.09874324083</v>
+        <v>68162.41930446583</v>
       </c>
       <c r="D5" t="n">
-        <v>10182965260.1505</v>
+        <v>5612685452.210941</v>
       </c>
       <c r="E5" t="n">
-        <v>92622.50812113671</v>
+        <v>73074.52462581106</v>
       </c>
     </row>
     <row r="6">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>156.0070094071375</v>
+        <v>11.6000436924513</v>
       </c>
       <c r="C6" t="n">
-        <v>307639.7905428354</v>
+        <v>54612.95461770775</v>
       </c>
       <c r="D6" t="n">
-        <v>467843780184.8976</v>
+        <v>4527768731.204343</v>
       </c>
       <c r="E6" t="n">
-        <v>377333.1911290791</v>
+        <v>64010.13576304898</v>
       </c>
     </row>
     <row r="7">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.56121856330116</v>
+        <v>18.91232115699927</v>
       </c>
       <c r="C7" t="n">
-        <v>129100.8113796894</v>
+        <v>96451.44822778925</v>
       </c>
       <c r="D7" t="n">
-        <v>21746735358.61444</v>
+        <v>11803929650.22195</v>
       </c>
       <c r="E7" t="n">
-        <v>133300.5980987916</v>
+        <v>101435.1949681867</v>
       </c>
     </row>
   </sheetData>
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.31881976591612</v>
+        <v>9.252252341581176</v>
       </c>
       <c r="C2" t="n">
-        <v>3742.066239795137</v>
+        <v>2520.105540674605</v>
       </c>
       <c r="D2" t="n">
-        <v>21871824.21105034</v>
+        <v>9992002.968848471</v>
       </c>
       <c r="E2" t="n">
-        <v>4132.457243307835</v>
+        <v>2938.010639040844</v>
       </c>
     </row>
     <row r="3">
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.60646974723173</v>
+        <v>6.73997696773422</v>
       </c>
       <c r="C3" t="n">
-        <v>2967.924597537879</v>
+        <v>1792.899820963542</v>
       </c>
       <c r="D3" t="n">
-        <v>16295730.95330255</v>
+        <v>5022857.920235792</v>
       </c>
       <c r="E3" t="n">
-        <v>3342.388562775222</v>
+        <v>2123.307510886405</v>
       </c>
     </row>
     <row r="4">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.92925676069356</v>
+        <v>12.89282623176919</v>
       </c>
       <c r="C4" t="n">
-        <v>3405.068870891293</v>
+        <v>3325.010846280526</v>
       </c>
       <c r="D4" t="n">
-        <v>15935621.66780804</v>
+        <v>15628153.00646107</v>
       </c>
       <c r="E4" t="n">
-        <v>3914.826230844692</v>
+        <v>3867.324300796254</v>
       </c>
     </row>
     <row r="5">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.61867197361728</v>
+        <v>16.36691977538839</v>
       </c>
       <c r="C5" t="n">
-        <v>4646.965003173231</v>
+        <v>4326.210089907468</v>
       </c>
       <c r="D5" t="n">
-        <v>28732448.98703677</v>
+        <v>25655249.07159467</v>
       </c>
       <c r="E5" t="n">
-        <v>5143.050137637239</v>
+        <v>4800.186980485244</v>
       </c>
     </row>
     <row r="6">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>535.4098016003874</v>
+        <v>18.12526833020848</v>
       </c>
       <c r="C6" t="n">
-        <v>74372.81119288964</v>
+        <v>4847.136889937747</v>
       </c>
       <c r="D6" t="n">
-        <v>27912040307.82309</v>
+        <v>44399438.24179521</v>
       </c>
       <c r="E6" t="n">
-        <v>87667.07529350465</v>
+        <v>5588.684940468375</v>
       </c>
     </row>
     <row r="7">
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.44026464357355</v>
+        <v>20.4475808990984</v>
       </c>
       <c r="C7" t="n">
-        <v>6707.9723494314</v>
+        <v>5610.703714941843</v>
       </c>
       <c r="D7" t="n">
-        <v>58928803.10135636</v>
+        <v>42993352.93612637</v>
       </c>
       <c r="E7" t="n">
-        <v>7254.898389047095</v>
+        <v>6239.511098973884</v>
       </c>
     </row>
   </sheetData>
